--- a/Extracted_data_analysis/tropical/Output-Transformed_data/summary_counts_question_1-3.xlsx
+++ b/Extracted_data_analysis/tropical/Output-Transformed_data/summary_counts_question_1-3.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="303">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="304">
   <si>
     <t xml:space="preserve">meso_substrate</t>
   </si>
@@ -609,7 +609,7 @@
     <t xml:space="preserve">Diversity+taxo</t>
   </si>
   <si>
-    <t xml:space="preserve">Diversity+taxonomy+geneticSequences</t>
+    <t xml:space="preserve">Diversity+taxo+geneticSequences</t>
   </si>
   <si>
     <t xml:space="preserve">Diversity+Trophic</t>
@@ -676,6 +676,9 @@
   </si>
   <si>
     <t xml:space="preserve">Health+Mortality+surv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Health+Physiological+surv</t>
   </si>
   <si>
     <t xml:space="preserve">Morphological</t>
@@ -1275,7 +1278,7 @@
         <v>10</v>
       </c>
       <c r="C2" t="n">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
     </row>
     <row r="3">
@@ -1286,7 +1289,7 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>0.5</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="4">
@@ -1294,10 +1297,10 @@
         <v>5</v>
       </c>
       <c r="B4" t="n">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="C4" t="n">
-        <v>71.04</v>
+        <v>71.39</v>
       </c>
     </row>
     <row r="5">
@@ -1308,7 +1311,7 @@
         <v>79</v>
       </c>
       <c r="C5" t="n">
-        <v>19.55</v>
+        <v>19.32</v>
       </c>
     </row>
     <row r="6">
@@ -1319,7 +1322,7 @@
         <v>19</v>
       </c>
       <c r="C6" t="n">
-        <v>4.7</v>
+        <v>4.65</v>
       </c>
     </row>
     <row r="7">
@@ -1330,7 +1333,7 @@
         <v>7</v>
       </c>
       <c r="C7" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
     </row>
   </sheetData>
@@ -1360,10 +1363,10 @@
         <v>6</v>
       </c>
       <c r="B2" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C2" t="n">
-        <v>17.05</v>
+        <v>17.16</v>
       </c>
     </row>
     <row r="3">
@@ -1371,10 +1374,10 @@
         <v>10</v>
       </c>
       <c r="B3" t="n">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="C3" t="n">
-        <v>74.32</v>
+        <v>74.27</v>
       </c>
     </row>
     <row r="4">
@@ -1385,7 +1388,7 @@
         <v>38</v>
       </c>
       <c r="C4" t="n">
-        <v>8.64</v>
+        <v>8.58</v>
       </c>
     </row>
   </sheetData>
@@ -1440,7 +1443,7 @@
         <v>44</v>
       </c>
       <c r="C4" t="n">
-        <v>9.98</v>
+        <v>9.91</v>
       </c>
     </row>
     <row r="5">
@@ -1451,7 +1454,7 @@
         <v>6</v>
       </c>
       <c r="C5" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
     </row>
     <row r="6">
@@ -1462,7 +1465,7 @@
         <v>7</v>
       </c>
       <c r="C6" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
     </row>
     <row r="7">
@@ -1470,10 +1473,10 @@
         <v>18</v>
       </c>
       <c r="B7" t="n">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="C7" t="n">
-        <v>85.71</v>
+        <v>85.81</v>
       </c>
     </row>
     <row r="8">
@@ -1525,10 +1528,10 @@
         <v>21</v>
       </c>
       <c r="B2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C2" t="n">
-        <v>5.43</v>
+        <v>5.62</v>
       </c>
     </row>
     <row r="3">
@@ -1539,7 +1542,7 @@
         <v>41</v>
       </c>
       <c r="C3" t="n">
-        <v>9.28</v>
+        <v>9.21</v>
       </c>
     </row>
     <row r="4">
@@ -1547,10 +1550,10 @@
         <v>23</v>
       </c>
       <c r="B4" t="n">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="C4" t="n">
-        <v>85.29</v>
+        <v>85.17</v>
       </c>
     </row>
   </sheetData>
@@ -1580,10 +1583,10 @@
         <v>25</v>
       </c>
       <c r="B2" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C2" t="n">
-        <v>18.45</v>
+        <v>18.55</v>
       </c>
     </row>
     <row r="3">
@@ -1594,7 +1597,7 @@
         <v>25</v>
       </c>
       <c r="C3" t="n">
-        <v>5.69</v>
+        <v>5.66</v>
       </c>
     </row>
     <row r="4">
@@ -1605,7 +1608,7 @@
         <v>11</v>
       </c>
       <c r="C4" t="n">
-        <v>2.51</v>
+        <v>2.49</v>
       </c>
     </row>
     <row r="5">
@@ -1613,10 +1616,10 @@
         <v>28</v>
       </c>
       <c r="B5" t="n">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C5" t="n">
-        <v>31.66</v>
+        <v>31.67</v>
       </c>
     </row>
     <row r="6">
@@ -1627,7 +1630,7 @@
         <v>4</v>
       </c>
       <c r="C6" t="n">
-        <v>0.91</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="7">
@@ -1638,7 +1641,7 @@
         <v>29</v>
       </c>
       <c r="C7" t="n">
-        <v>6.61</v>
+        <v>6.56</v>
       </c>
     </row>
     <row r="8">
@@ -1646,10 +1649,10 @@
         <v>31</v>
       </c>
       <c r="B8" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C8" t="n">
-        <v>19.59</v>
+        <v>19.68</v>
       </c>
     </row>
     <row r="9">
@@ -1671,7 +1674,7 @@
         <v>63</v>
       </c>
       <c r="C10" t="n">
-        <v>14.35</v>
+        <v>14.25</v>
       </c>
     </row>
   </sheetData>
@@ -1704,7 +1707,7 @@
         <v>14</v>
       </c>
       <c r="C2" t="n">
-        <v>3.2</v>
+        <v>3.17</v>
       </c>
     </row>
     <row r="3">
@@ -1814,7 +1817,7 @@
         <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>0.46</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="13">
@@ -1946,7 +1949,7 @@
         <v>2</v>
       </c>
       <c r="C24" t="n">
-        <v>0.46</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="25">
@@ -2001,7 +2004,7 @@
         <v>5</v>
       </c>
       <c r="C29" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
     </row>
     <row r="30">
@@ -2111,7 +2114,7 @@
         <v>2</v>
       </c>
       <c r="C39" t="n">
-        <v>0.46</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="40">
@@ -2254,7 +2257,7 @@
         <v>9</v>
       </c>
       <c r="C52" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
     </row>
     <row r="53">
@@ -2273,10 +2276,10 @@
         <v>87</v>
       </c>
       <c r="B54" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C54" t="n">
-        <v>0.68</v>
+        <v>0.91</v>
       </c>
     </row>
     <row r="55">
@@ -2485,7 +2488,7 @@
         <v>2</v>
       </c>
       <c r="C73" t="n">
-        <v>0.46</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="74">
@@ -2573,7 +2576,7 @@
         <v>2</v>
       </c>
       <c r="C81" t="n">
-        <v>0.46</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="82">
@@ -2691,10 +2694,10 @@
         <v>125</v>
       </c>
       <c r="B92" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C92" t="n">
-        <v>1.83</v>
+        <v>2.04</v>
       </c>
     </row>
     <row r="93">
@@ -2793,7 +2796,7 @@
         <v>10</v>
       </c>
       <c r="C101" t="n">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
     </row>
     <row r="102">
@@ -2815,7 +2818,7 @@
         <v>2</v>
       </c>
       <c r="C103" t="n">
-        <v>0.46</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="104">
@@ -2837,7 +2840,7 @@
         <v>2</v>
       </c>
       <c r="C105" t="n">
-        <v>0.46</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="106">
@@ -2859,7 +2862,7 @@
         <v>8</v>
       </c>
       <c r="C107" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
     </row>
     <row r="108">
@@ -2903,7 +2906,7 @@
         <v>2</v>
       </c>
       <c r="C111" t="n">
-        <v>0.46</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="112">
@@ -2914,7 +2917,7 @@
         <v>6</v>
       </c>
       <c r="C112" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
     </row>
     <row r="113">
@@ -2947,7 +2950,7 @@
         <v>2</v>
       </c>
       <c r="C115" t="n">
-        <v>0.46</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="116">
@@ -3002,7 +3005,7 @@
         <v>2</v>
       </c>
       <c r="C120" t="n">
-        <v>0.46</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="121">
@@ -3057,7 +3060,7 @@
         <v>2</v>
       </c>
       <c r="C125" t="n">
-        <v>0.46</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="126">
@@ -3068,7 +3071,7 @@
         <v>2</v>
       </c>
       <c r="C126" t="n">
-        <v>0.46</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="127">
@@ -3079,7 +3082,7 @@
         <v>2</v>
       </c>
       <c r="C127" t="n">
-        <v>0.46</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="128">
@@ -3090,7 +3093,7 @@
         <v>2</v>
       </c>
       <c r="C128" t="n">
-        <v>0.46</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="129">
@@ -3112,7 +3115,7 @@
         <v>2</v>
       </c>
       <c r="C130" t="n">
-        <v>0.46</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="131">
@@ -3277,7 +3280,7 @@
         <v>12</v>
       </c>
       <c r="C145" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
     </row>
     <row r="146">
@@ -3288,7 +3291,7 @@
         <v>16</v>
       </c>
       <c r="C146" t="n">
-        <v>3.65</v>
+        <v>3.63</v>
       </c>
     </row>
     <row r="147">
@@ -3343,7 +3346,7 @@
         <v>2</v>
       </c>
       <c r="C151" t="n">
-        <v>0.46</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="152">
@@ -3409,7 +3412,7 @@
         <v>15</v>
       </c>
       <c r="C157" t="n">
-        <v>3.42</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="158">
@@ -3420,7 +3423,7 @@
         <v>2</v>
       </c>
       <c r="C158" t="n">
-        <v>0.46</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="159">
@@ -3442,7 +3445,7 @@
         <v>2</v>
       </c>
       <c r="C160" t="n">
-        <v>0.46</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="161">
@@ -3541,7 +3544,7 @@
         <v>2</v>
       </c>
       <c r="C169" t="n">
-        <v>0.46</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="170">
@@ -3725,10 +3728,10 @@
         <v>219</v>
       </c>
       <c r="B186" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C186" t="n">
-        <v>0.46</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="187">
@@ -3736,10 +3739,10 @@
         <v>220</v>
       </c>
       <c r="B187" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C187" t="n">
-        <v>0.23</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="188">
@@ -3747,10 +3750,10 @@
         <v>221</v>
       </c>
       <c r="B188" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C188" t="n">
-        <v>1.37</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="189">
@@ -3758,10 +3761,10 @@
         <v>222</v>
       </c>
       <c r="B189" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C189" t="n">
-        <v>0.23</v>
+        <v>1.36</v>
       </c>
     </row>
     <row r="190">
@@ -3791,10 +3794,10 @@
         <v>225</v>
       </c>
       <c r="B192" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C192" t="n">
-        <v>0.46</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="193">
@@ -3805,7 +3808,7 @@
         <v>2</v>
       </c>
       <c r="C193" t="n">
-        <v>0.46</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="194">
@@ -3816,7 +3819,7 @@
         <v>2</v>
       </c>
       <c r="C194" t="n">
-        <v>0.46</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="195">
@@ -3824,10 +3827,10 @@
         <v>228</v>
       </c>
       <c r="B195" t="n">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="C195" t="n">
-        <v>7.76</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="196">
@@ -3835,10 +3838,10 @@
         <v>229</v>
       </c>
       <c r="B196" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C196" t="n">
-        <v>6.85</v>
+        <v>7.71</v>
       </c>
     </row>
     <row r="197">
@@ -3846,10 +3849,10 @@
         <v>230</v>
       </c>
       <c r="B197" t="n">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="C197" t="n">
-        <v>0.23</v>
+        <v>7.03</v>
       </c>
     </row>
     <row r="198">
@@ -3945,10 +3948,10 @@
         <v>239</v>
       </c>
       <c r="B206" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C206" t="n">
-        <v>1.6</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="207">
@@ -3956,10 +3959,10 @@
         <v>240</v>
       </c>
       <c r="B207" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C207" t="n">
-        <v>1.14</v>
+        <v>1.59</v>
       </c>
     </row>
     <row r="208">
@@ -3967,10 +3970,10 @@
         <v>241</v>
       </c>
       <c r="B208" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C208" t="n">
-        <v>0.23</v>
+        <v>0.91</v>
       </c>
     </row>
     <row r="209">
@@ -4022,10 +4025,10 @@
         <v>246</v>
       </c>
       <c r="B213" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C213" t="n">
-        <v>0.46</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="214">
@@ -4033,10 +4036,10 @@
         <v>247</v>
       </c>
       <c r="B214" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C214" t="n">
-        <v>0.23</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="215">
@@ -4044,10 +4047,10 @@
         <v>248</v>
       </c>
       <c r="B215" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C215" t="n">
-        <v>0.68</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="216">
@@ -4055,10 +4058,10 @@
         <v>249</v>
       </c>
       <c r="B216" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C216" t="n">
-        <v>0.23</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="217">
@@ -4066,10 +4069,10 @@
         <v>250</v>
       </c>
       <c r="B217" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C217" t="n">
-        <v>0.91</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="218">
@@ -4077,9 +4080,20 @@
         <v>251</v>
       </c>
       <c r="B218" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C218" t="n">
+        <v>0.91</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="s">
+        <v>252</v>
+      </c>
+      <c r="B219" t="n">
+        <v>1</v>
+      </c>
+      <c r="C219" t="n">
         <v>0.23</v>
       </c>
     </row>
@@ -4096,7 +4110,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
@@ -4107,62 +4121,62 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B2" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C2" t="n">
-        <v>10.63</v>
+        <v>11.01</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B3" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C3" t="n">
-        <v>11.31</v>
+        <v>11.46</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B4" t="n">
         <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B5" t="n">
         <v>3</v>
       </c>
       <c r="C5" t="n">
-        <v>0.68</v>
+        <v>0.67</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B6" t="n">
         <v>9</v>
       </c>
       <c r="C6" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B7" t="n">
         <v>4</v>
@@ -4173,40 +4187,40 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B8" t="n">
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B9" t="n">
         <v>1</v>
       </c>
       <c r="C9" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B10" t="n">
         <v>14</v>
       </c>
       <c r="C10" t="n">
-        <v>3.17</v>
+        <v>3.15</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B11" t="n">
         <v>4</v>
@@ -4217,40 +4231,40 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B12" t="n">
         <v>7</v>
       </c>
       <c r="C12" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B13" t="n">
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B14" t="n">
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B15" t="n">
         <v>2</v>
@@ -4261,18 +4275,18 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B16" t="n">
         <v>172</v>
       </c>
       <c r="C16" t="n">
-        <v>38.91</v>
+        <v>38.65</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B17" t="n">
         <v>2</v>
@@ -4283,84 +4297,84 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B18" t="n">
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B19" t="n">
         <v>1</v>
       </c>
       <c r="C19" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B20" t="n">
         <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B21" t="n">
         <v>28</v>
       </c>
       <c r="C21" t="n">
-        <v>6.33</v>
+        <v>6.29</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B22" t="n">
         <v>3</v>
       </c>
       <c r="C22" t="n">
-        <v>0.68</v>
+        <v>0.67</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B23" t="n">
         <v>1</v>
       </c>
       <c r="C23" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B24" t="n">
         <v>13</v>
       </c>
       <c r="C24" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B25" t="n">
         <v>2</v>
@@ -4371,7 +4385,7 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B26" t="n">
         <v>2</v>
@@ -4382,46 +4396,46 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B27" t="n">
         <v>47</v>
       </c>
       <c r="C27" t="n">
-        <v>10.63</v>
+        <v>10.56</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B28" t="n">
         <v>8</v>
       </c>
       <c r="C28" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B29" t="n">
         <v>9</v>
       </c>
       <c r="C29" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B30" t="n">
         <v>1</v>
       </c>
       <c r="C30" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
     </row>
   </sheetData>
@@ -4437,7 +4451,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
@@ -4448,18 +4462,18 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B2" t="n">
         <v>10</v>
       </c>
       <c r="C2" t="n">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B3" t="n">
         <v>1</v>
@@ -4470,84 +4484,84 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B4" t="n">
         <v>2</v>
       </c>
       <c r="C4" t="n">
-        <v>0.46</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B5" t="n">
         <v>3</v>
       </c>
       <c r="C5" t="n">
-        <v>0.69</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>1.37</v>
+        <v>1.14</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B7" t="n">
         <v>2</v>
       </c>
       <c r="C7" t="n">
-        <v>0.46</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B8" t="n">
         <v>3</v>
       </c>
       <c r="C8" t="n">
-        <v>0.69</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B9" t="n">
         <v>36</v>
       </c>
       <c r="C9" t="n">
-        <v>8.24</v>
+        <v>8.18</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B10" t="n">
         <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>0.69</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B11" t="n">
         <v>1</v>
@@ -4558,18 +4572,18 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B12" t="n">
         <v>13</v>
       </c>
       <c r="C12" t="n">
-        <v>2.97</v>
+        <v>2.95</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B13" t="n">
         <v>1</v>
@@ -4580,7 +4594,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B14" t="n">
         <v>1</v>
@@ -4591,18 +4605,18 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B15" t="n">
         <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>0.69</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B16" t="n">
         <v>1</v>
@@ -4624,29 +4638,29 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B18" t="n">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="C18" t="n">
-        <v>72.31</v>
+        <v>72.73</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B19" t="n">
         <v>21</v>
       </c>
       <c r="C19" t="n">
-        <v>4.81</v>
+        <v>4.77</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B20" t="n">
         <v>5</v>
@@ -4657,24 +4671,24 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B21" t="n">
         <v>2</v>
       </c>
       <c r="C21" t="n">
-        <v>0.46</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B22" t="n">
         <v>6</v>
       </c>
       <c r="C22" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
     </row>
   </sheetData>
